--- a/config/email_farmaconde.xlsx
+++ b/config/email_farmaconde.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BI - SENFF SHOPPING\Relatorios_API-VTEX\VENDAS_FATURADAS\FARMA CONDE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.chagas\Documents\farma_conde_0826\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C5D9C4-A787-4B56-B8C3-3FC77C0A0A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5647C9-C242-4D93-BC99-43A25041BDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
     <t>sim</t>
   </si>
   <si>
-    <t>a.chagas@senff.com.br;l.ruiz@senff.com.br;samir.nadir@grupofarmaconde.com.br;danilo.fernandes@grupofarmaconde.com.br;valeska.amorim@grupofarmaconde.com.br</t>
+    <t>a.chagas@senff.com.br;l.ruiz@senff.com.br;samir.nadir@grupofarmaconde.com.br;valeska.amorim@grupofarmaconde.com.br;l.wolck@senff.com.br</t>
   </si>
 </sst>
 </file>

--- a/config/email_farmaconde.xlsx
+++ b/config/email_farmaconde.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.chagas\Documents\farma_conde_0826\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5647C9-C242-4D93-BC99-43A25041BDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5924AB87-FEAE-4110-A9F9-FEAF569A9007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
     <t>sim</t>
   </si>
   <si>
-    <t>a.chagas@senff.com.br;l.ruiz@senff.com.br;samir.nadir@grupofarmaconde.com.br;valeska.amorim@grupofarmaconde.com.br;l.wolck@senff.com.br</t>
+    <t>a.chagas@senff.com.br;l.ruiz@senff.com.br;contasareceber@grupofarmaconde.com.br;samir.nadir@grupofarmaconde.com.br;l.wolck@senff.com.br</t>
   </si>
 </sst>
 </file>
